--- a/worked_examples/AIHE-CASE10_patient_facing_chatbot_institutional_risk_review/workbook/xlsx/AIHE-CASE10_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE10_patient_facing_chatbot_institutional_risk_review/workbook/xlsx/AIHE-CASE10_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Reed9d0d93f8e46c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="Rc4b3b1e8fa844713"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R79da29ac9eac441f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R00140b4d96804300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R3696d1617dbd41ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R4245c1accfa94f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R6ae64b59331b40fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R0d842ff1ec914a75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="36">
     <x:border/>
@@ -369,7 +385,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -378,7 +394,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -386,7 +402,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,22 +419,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -435,22 +451,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -495,22 +511,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -525,22 +541,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -611,6 +627,53 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -663,9 +726,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -774,25 +837,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Patient-Facing Chatbot Institutional-Risk Review</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="104" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -800,7 +863,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="106" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -808,7 +871,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="106" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -816,7 +879,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="106" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -824,7 +887,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="106" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -832,7 +895,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="106" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -840,7 +903,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="106" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -848,7 +911,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="106" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -856,7 +919,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="108" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -888,48 +951,48 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
+      <x:c r="G1" s="102"/>
+      <x:c r="H1" s="102"/>
+      <x:c r="I1" s="102"/>
+      <x:c r="J1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Risk</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Likelihood</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Impact</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Control effectiveness</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="114" t="str">
         <x:v>Mandatory concern</x:v>
       </x:c>
-      <x:c r="F3" s="57" t="str">
+      <x:c r="F3" s="112" t="str">
         <x:v>Inherent risk</x:v>
       </x:c>
-      <x:c r="G3" s="58" t="str">
+      <x:c r="G3" s="113" t="str">
         <x:v>Residual risk</x:v>
       </x:c>
-      <x:c r="H3" s="59" t="str">
+      <x:c r="H3" s="114" t="str">
         <x:v>Mandatory residual concern</x:v>
       </x:c>
-      <x:c r="J3" s="57" t="str">
+      <x:c r="J3" s="112" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="K3" s="59" t="str">
+      <x:c r="K3" s="114" t="str">
         <x:v>Formula result</x:v>
       </x:c>
     </x:row>
@@ -1169,28 +1232,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Risk</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Likelihood</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Impact</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Control effectiveness</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="114" t="str">
         <x:v>Mandatory concern</x:v>
       </x:c>
     </x:row>
@@ -1292,28 +1355,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Patient-Facing Chatbot Institutional-Risk Review</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="114" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1334,66 +1397,66 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="89" t="str">
+      <x:c r="A8" s="115" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B8" s="89"/>
-      <x:c r="C8" s="89"/>
-      <x:c r="D8" s="89"/>
-      <x:c r="E8" s="89"/>
-      <x:c r="F8" s="89"/>
+      <x:c r="B8" s="115"/>
+      <x:c r="C8" s="115"/>
+      <x:c r="D8" s="115"/>
+      <x:c r="E8" s="115"/>
+      <x:c r="F8" s="115"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="94" t="str">
+      <x:c r="A9" s="116" t="str">
         <x:v>The review does not support unrestricted symptom navigation. Several mandatory concerns remain high, especially unsupported advice, escalation failure, and digital exclusion. The chatbot may be piloted for bounded administrative functions using approved content, disclosure, rapid human escalation, accessible alternatives, minimum data collection, and continuous monitoring.</x:v>
       </x:c>
-      <x:c r="B9" s="94"/>
-      <x:c r="C9" s="94"/>
-      <x:c r="D9" s="94"/>
-      <x:c r="E9" s="94"/>
-      <x:c r="F9" s="94"/>
+      <x:c r="B9" s="116"/>
+      <x:c r="C9" s="116"/>
+      <x:c r="D9" s="116"/>
+      <x:c r="E9" s="116"/>
+      <x:c r="F9" s="116"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="94"/>
-      <x:c r="B10" s="94"/>
-      <x:c r="C10" s="94"/>
-      <x:c r="D10" s="94"/>
-      <x:c r="E10" s="94"/>
-      <x:c r="F10" s="94"/>
+      <x:c r="A10" s="116"/>
+      <x:c r="B10" s="116"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
+      <x:c r="E10" s="116"/>
+      <x:c r="F10" s="116"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="94"/>
-      <x:c r="B11" s="94"/>
-      <x:c r="C11" s="94"/>
-      <x:c r="D11" s="94"/>
-      <x:c r="E11" s="94"/>
-      <x:c r="F11" s="94"/>
+      <x:c r="A11" s="116"/>
+      <x:c r="B11" s="116"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
+      <x:c r="E11" s="116"/>
+      <x:c r="F11" s="116"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="94"/>
-      <x:c r="B12" s="94"/>
-      <x:c r="C12" s="94"/>
-      <x:c r="D12" s="94"/>
-      <x:c r="E12" s="94"/>
-      <x:c r="F12" s="94"/>
+      <x:c r="A12" s="116"/>
+      <x:c r="B12" s="116"/>
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="116"/>
+      <x:c r="E12" s="116"/>
+      <x:c r="F12" s="116"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="94"/>
-      <x:c r="B13" s="94"/>
-      <x:c r="C13" s="94"/>
-      <x:c r="D13" s="94"/>
-      <x:c r="E13" s="94"/>
-      <x:c r="F13" s="94"/>
+      <x:c r="A13" s="116"/>
+      <x:c r="B13" s="116"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
+      <x:c r="E13" s="116"/>
+      <x:c r="F13" s="116"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="100" t="str">
+      <x:c r="A15" s="117" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B15" s="100"/>
-      <x:c r="C15" s="100"/>
-      <x:c r="D15" s="100"/>
-      <x:c r="E15" s="100"/>
-      <x:c r="F15" s="100"/>
+      <x:c r="B15" s="117"/>
+      <x:c r="C15" s="117"/>
+      <x:c r="D15" s="117"/>
+      <x:c r="E15" s="117"/>
+      <x:c r="F15" s="117"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
